--- a/outputs/daily/hr_rankings_2026-07-29_remaining.xlsx
+++ b/outputs/daily/hr_rankings_2026-07-29_remaining.xlsx
@@ -1320,7 +1320,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -1880,7 +1880,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -2440,7 +2440,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -2720,7 +2720,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -4400,7 +4400,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -4960,7 +4960,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -5800,7 +5800,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -6920,7 +6920,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -7200,7 +7200,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -7480,7 +7480,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -7760,7 +7760,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -8040,7 +8040,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -8880,7 +8880,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -9160,7 +9160,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -9440,7 +9440,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -10000,7 +10000,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -11120,7 +11120,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -11680,7 +11680,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -11960,7 +11960,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -12520,7 +12520,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -13080,7 +13080,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -13360,7 +13360,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -13920,7 +13920,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -14760,7 +14760,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -15040,7 +15040,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -15320,7 +15320,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -15880,7 +15880,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -16160,7 +16160,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -16720,7 +16720,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -17000,7 +17000,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -17840,7 +17840,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -18400,7 +18400,7 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -18960,7 +18960,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -20080,7 +20080,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -20640,7 +20640,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -21760,7 +21760,7 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
@@ -22040,7 +22040,7 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
@@ -22880,7 +22880,7 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
@@ -23160,7 +23160,7 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
@@ -23440,7 +23440,7 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
@@ -24000,7 +24000,7 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
@@ -24280,7 +24280,7 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
@@ -25400,7 +25400,7 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
@@ -25680,7 +25680,7 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
@@ -26240,7 +26240,7 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
@@ -26520,7 +26520,7 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
@@ -27080,7 +27080,7 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
@@ -27360,7 +27360,7 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
@@ -27640,7 +27640,7 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
@@ -28760,7 +28760,7 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
@@ -29320,7 +29320,7 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
@@ -29600,7 +29600,7 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
@@ -29880,7 +29880,7 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
@@ -30160,7 +30160,7 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
@@ -31886,7 +31886,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -32446,7 +32446,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -33006,7 +33006,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -33286,7 +33286,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -34966,7 +34966,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -35526,7 +35526,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -36366,7 +36366,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
